--- a/artfynd/A 14344-2025 artfynd.xlsx
+++ b/artfynd/A 14344-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>79257554</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470462.8847213312</v>
+        <v>470463</v>
       </c>
       <c r="R2" t="n">
-        <v>6973365.321125035</v>
+        <v>6973365</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +747,9 @@
           <t>2019-07-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-07-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +780,7 @@
         <v>79257552</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470462.8847213312</v>
+        <v>470463</v>
       </c>
       <c r="R3" t="n">
-        <v>6973365.321125035</v>
+        <v>6973365</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +849,9 @@
           <t>2019-07-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-07-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
